--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/lib-gral-bdo-o-higgins.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/lib-gral-bdo-o-higgins.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>12564.01</v>
+        <v>12495.33</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7881.74</v>
+        <v>7909.87</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>14803.32</v>
+        <v>14780.37</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5540.4</v>
+        <v>5531.81</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5740.17</v>
+        <v>5780.68</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>15719.58</v>
+        <v>15827.78</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>16606.09</v>
+        <v>16671.56</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7395.24</v>
+        <v>7347.86</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>29699.76</v>
+        <v>30430.67</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>11472.23</v>
+        <v>11507.69</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>50344.22</v>
+        <v>50822.44</v>
       </c>
     </row>
   </sheetData>
